--- a/Indomie Clients Details/Raheem/Raheem Store Iqbal Town.xlsx
+++ b/Indomie Clients Details/Raheem/Raheem Store Iqbal Town.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C7611A-6970-426A-9DC5-0553A5E74489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCDCCEE-C5F7-4DD0-B17E-E2F2CB110458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -384,9 +384,6 @@
     <t>Shakoor</t>
   </si>
   <si>
-    <t>Vacant__LMT</t>
-  </si>
-  <si>
     <t>Shop Bill Summary (LMT)</t>
   </si>
   <si>
@@ -397,6 +394,9 @@
   </si>
   <si>
     <t>A244322-8</t>
+  </si>
+  <si>
+    <t>Raheem Iqbal Town</t>
   </si>
 </sst>
 </file>
@@ -3379,7 +3379,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -3394,7 +3394,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -3407,7 +3407,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -3416,7 +3416,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -3500,7 +3500,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="168" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -4624,7 +4624,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -4639,7 +4639,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -4652,7 +4652,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -4661,7 +4661,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -4745,7 +4745,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -5869,7 +5869,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -5884,7 +5884,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -5897,7 +5897,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -5990,7 +5990,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="166" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -7114,7 +7114,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -7129,7 +7129,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -7142,7 +7142,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -7151,7 +7151,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -7235,7 +7235,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -8359,7 +8359,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -8374,7 +8374,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -8387,7 +8387,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -8396,7 +8396,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -8480,7 +8480,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -9604,7 +9604,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -9619,7 +9619,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -9632,7 +9632,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -9641,7 +9641,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -9725,7 +9725,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -10849,7 +10849,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -10864,7 +10864,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -10877,7 +10877,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -10886,7 +10886,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -10970,7 +10970,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -12094,7 +12094,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -12109,7 +12109,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -12122,7 +12122,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -12131,7 +12131,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -12215,7 +12215,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -13339,7 +13339,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -13354,7 +13354,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -13367,7 +13367,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -13376,7 +13376,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -13460,7 +13460,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="179" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -14584,7 +14584,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -14599,7 +14599,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -14612,7 +14612,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -14621,7 +14621,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -14705,7 +14705,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -18579,7 +18579,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -18594,7 +18594,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -18607,7 +18607,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -18616,7 +18616,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -18700,7 +18700,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -19821,7 +19821,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -19836,7 +19836,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -19849,7 +19849,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -19858,7 +19858,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -19942,7 +19942,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -21062,7 +21062,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -21077,7 +21077,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -21090,7 +21090,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -21099,7 +21099,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -21183,7 +21183,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -22303,7 +22303,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -22318,7 +22318,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -22331,7 +22331,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -22340,7 +22340,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -22424,7 +22424,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -23549,7 +23549,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -23564,7 +23564,7 @@
     </row>
     <row r="5" spans="1:21 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="205" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B5" s="205"/>
       <c r="C5" s="205"/>
@@ -23577,7 +23577,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -23721,7 +23721,7 @@
       <c r="R12" s="70"/>
       <c r="S12" s="71"/>
       <c r="T12" s="216" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U12" s="217"/>
       <c r="XFD12" t="s">
@@ -23841,7 +23841,7 @@
       </c>
       <c r="U15" s="163">
         <f>+'2'!P35</f>
-        <v>0</v>
+        <v>36548.000689200002</v>
       </c>
       <c r="XFD15" t="s">
         <v>81</v>
@@ -23874,11 +23874,11 @@
       <c r="G16" s="113"/>
       <c r="H16" s="171">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16+'17'!H16+'18'!H16</f>
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>4197</v>
+        <v>10492.5</v>
       </c>
       <c r="J16" s="171">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16</f>
@@ -23890,23 +23890,23 @@
       </c>
       <c r="L16" s="174">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>587.58000000000004</v>
+        <v>1468.9500000000003</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>3609.42</v>
+        <v>9023.5499999999993</v>
       </c>
       <c r="N16" s="100">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>649.69560000000001</v>
+        <v>1624.239</v>
       </c>
       <c r="O16" s="100">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>21.295578000000003</v>
+        <v>53.238945000000001</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>4280.4111780000003</v>
+        <v>10701.027944999998</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="T16" s="162" t="str">
@@ -23948,11 +23948,11 @@
       <c r="G17" s="113"/>
       <c r="H17" s="171">
         <f>+'1'!H17+'2'!H17+'4'!H17+'3'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17+'17'!H17+'18'!H17</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ref="I17:I23" si="1">(G17*D17)*F17+H17*F17</f>
-        <v>0</v>
+        <v>6295.5</v>
       </c>
       <c r="J17" s="171">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17</f>
@@ -23964,23 +23964,23 @@
       </c>
       <c r="L17" s="174">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>0</v>
+        <v>881.37000000000012</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>0</v>
+        <v>5414.13</v>
       </c>
       <c r="N17" s="100">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>0</v>
+        <v>974.54340000000002</v>
       </c>
       <c r="O17" s="100">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>0</v>
+        <v>31.943366999999999</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6420.6167669999995</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="162" t="str">
@@ -24092,11 +24092,11 @@
       <c r="G19" s="113"/>
       <c r="H19" s="171">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19+'17'!H19+'18'!H19</f>
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>14528</v>
+        <v>26150.400000000001</v>
       </c>
       <c r="J19" s="171">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
@@ -24108,23 +24108,23 @@
       </c>
       <c r="L19" s="174">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>2033.9200000000003</v>
+        <v>3661.0560000000005</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="2"/>
-        <v>12494.08</v>
+        <v>22489.344000000001</v>
       </c>
       <c r="N19" s="100">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>2248.9344000000001</v>
+        <v>4048.0819199999996</v>
       </c>
       <c r="O19" s="100">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>73.715072000000006</v>
+        <v>132.68712959999999</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="0"/>
-        <v>14816.729472000001</v>
+        <v>26670.113049600001</v>
       </c>
       <c r="T19" s="162" t="str">
         <f>+'6'!A5</f>
@@ -24232,11 +24232,11 @@
       <c r="G21" s="113"/>
       <c r="H21" s="171">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21+'17'!H21+'18'!H21</f>
-        <v>400</v>
+        <v>560</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>29056</v>
+        <v>40678.400000000001</v>
       </c>
       <c r="J21" s="171">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
@@ -24248,23 +24248,23 @@
       </c>
       <c r="L21" s="174">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>4067.8400000000006</v>
+        <v>5694.9760000000006</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="2"/>
-        <v>24988.16</v>
+        <v>34983.423999999999</v>
       </c>
       <c r="N21" s="100">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>4497.8688000000002</v>
+        <v>6297.0163199999997</v>
       </c>
       <c r="O21" s="100">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>147.43014400000001</v>
+        <v>206.40220160000001</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="0"/>
-        <v>29633.458944000002</v>
+        <v>41486.842521600003</v>
       </c>
       <c r="T21" s="162" t="str">
         <f>+'8'!A5</f>
@@ -24492,7 +24492,7 @@
       <c r="B25" s="227"/>
       <c r="C25" s="228">
         <f>H25/40</f>
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D25" s="222"/>
       <c r="E25" s="222"/>
@@ -24503,11 +24503,11 @@
       </c>
       <c r="H25" s="176">
         <f t="shared" si="3"/>
-        <v>880</v>
+        <v>1440</v>
       </c>
       <c r="I25" s="177">
         <f t="shared" si="3"/>
-        <v>58273.5</v>
+        <v>94109.3</v>
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
@@ -24519,23 +24519,23 @@
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>8158.2900000000009</v>
+        <v>13175.302000000001</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>50115.21</v>
+        <v>80933.997999999992</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>9020.737799999999</v>
+        <v>14568.119639999997</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>295.67973900000004</v>
+        <v>477.51058820000003</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>59431.627539000001</v>
+        <v>95979.628228200003</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24743,7 +24743,7 @@
       </c>
       <c r="U33" s="164">
         <f>SUM(U14:U28)</f>
-        <v>59431.627538999994</v>
+        <v>95979.628228199988</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24776,7 +24776,7 @@
       <c r="O35" s="239"/>
       <c r="P35" s="151">
         <f>I25</f>
-        <v>58273.5</v>
+        <v>94109.3</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24797,7 +24797,7 @@
       <c r="O36" s="241"/>
       <c r="P36" s="152">
         <f>L25</f>
-        <v>8158.2900000000009</v>
+        <v>13175.302000000001</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24840,7 +24840,7 @@
       <c r="O38" s="241"/>
       <c r="P38" s="152">
         <f>P35-P36-P37</f>
-        <v>50115.21</v>
+        <v>80933.998000000007</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24865,7 +24865,7 @@
       </c>
       <c r="P39" s="152">
         <f>N25</f>
-        <v>9020.737799999999</v>
+        <v>14568.119639999997</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24887,7 +24887,7 @@
       <c r="O40" s="243"/>
       <c r="P40" s="152">
         <f>P38+P39</f>
-        <v>59135.947799999994</v>
+        <v>95502.117640000011</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24912,7 +24912,7 @@
       </c>
       <c r="P41" s="152">
         <f>O41*P40</f>
-        <v>1478.3986949999999</v>
+        <v>2387.5529410000004</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24922,7 +24922,7 @@
       <c r="O42" s="221"/>
       <c r="P42" s="159">
         <f>P40+P41</f>
-        <v>60614.346494999991</v>
+        <v>97889.670581000013</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25094,7 +25094,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -25109,7 +25109,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -25122,7 +25122,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -25131,7 +25131,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -25215,7 +25215,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -25482,22 +25482,22 @@
         <v>0</v>
       </c>
       <c r="I17" s="115">
-        <f t="shared" ref="I17:I23" si="3">(G17*D17)*F17+H17*F17</f>
+        <f>(G17*D17)*F17+H17*F17</f>
         <v>0</v>
       </c>
       <c r="J17" s="116">
         <v>0</v>
       </c>
       <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="4">I17*$K$13</f>
+        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="5">I17*14%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*14%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
-        <f t="shared" ref="M17:M23" si="6">I17-K17-L17</f>
+        <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
         <v>0</v>
       </c>
       <c r="N17" s="117">
@@ -25546,22 +25546,22 @@
         <v>200</v>
       </c>
       <c r="I18" s="115">
+        <f>(G18*D18)*F18+H18*F18</f>
+        <v>10492.5</v>
+      </c>
+      <c r="J18" s="116">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
         <f t="shared" si="3"/>
-        <v>10492.5</v>
-      </c>
-      <c r="J18" s="116">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="104">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="104">
+        <v>1468.95</v>
+      </c>
+      <c r="M18" s="117">
         <f t="shared" si="5"/>
-        <v>1468.95</v>
-      </c>
-      <c r="M18" s="117">
-        <f t="shared" si="6"/>
         <v>9023.5499999999993</v>
       </c>
       <c r="N18" s="117">
@@ -25606,22 +25606,22 @@
         <v>200</v>
       </c>
       <c r="I19" s="115">
+        <f>(G19*D19)*F19+H19*F19</f>
+        <v>14528</v>
+      </c>
+      <c r="J19" s="116">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
         <f t="shared" si="3"/>
-        <v>14528</v>
-      </c>
-      <c r="J19" s="116">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="104">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="104">
+        <v>2033.9200000000003</v>
+      </c>
+      <c r="M19" s="117">
         <f t="shared" si="5"/>
-        <v>2033.9200000000003</v>
-      </c>
-      <c r="M19" s="117">
-        <f t="shared" si="6"/>
         <v>12494.08</v>
       </c>
       <c r="N19" s="117">
@@ -25666,22 +25666,22 @@
         <v>0</v>
       </c>
       <c r="I20" s="115">
+        <f>(G20*D20)*F20+H20*F20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="116">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J20" s="116">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="L20" s="104">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L20" s="104">
+      <c r="M20" s="117">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="117">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N20" s="117">
@@ -25726,22 +25726,22 @@
         <v>400</v>
       </c>
       <c r="I21" s="115">
+        <f>(G21*D21)*F21+H21*F21</f>
+        <v>29056</v>
+      </c>
+      <c r="J21" s="116">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
         <f t="shared" si="3"/>
-        <v>29056</v>
-      </c>
-      <c r="J21" s="116">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="104">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="104">
+        <v>4067.8400000000006</v>
+      </c>
+      <c r="M21" s="117">
         <f t="shared" si="5"/>
-        <v>4067.8400000000006</v>
-      </c>
-      <c r="M21" s="117">
-        <f t="shared" si="6"/>
         <v>24988.16</v>
       </c>
       <c r="N21" s="117">
@@ -25786,7 +25786,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="115">
-        <f t="shared" si="3"/>
+        <f>(G22*D22)*F22+H22*F22</f>
         <v>0</v>
       </c>
       <c r="J22" s="116"/>
@@ -25799,7 +25799,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="117">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N22" s="117">
@@ -25842,7 +25842,7 @@
       <c r="G23" s="113"/>
       <c r="H23" s="114"/>
       <c r="I23" s="115">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="I23" si="6">(G23*D23)*F23+H23*F23</f>
         <v>0</v>
       </c>
       <c r="J23" s="116"/>
@@ -25855,7 +25855,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="117">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N23" s="117">
@@ -25941,7 +25941,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="135">
-        <f t="shared" si="9"/>
+        <f>SUM(H16:H24)</f>
         <v>880</v>
       </c>
       <c r="I25" s="136">
@@ -26314,7 +26314,7 @@
       <c r="L3" s="202"/>
       <c r="M3" s="202"/>
       <c r="N3" s="201">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="O3" s="201"/>
       <c r="P3" s="201"/>
@@ -26342,7 +26342,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -26357,7 +26357,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -26370,7 +26370,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -26379,7 +26379,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -26391,7 +26391,7 @@
       <c r="L6" s="202"/>
       <c r="M6" s="202"/>
       <c r="N6" s="204" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="O6" s="204"/>
       <c r="P6" s="204"/>
@@ -26463,7 +26463,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -26487,11 +26487,11 @@
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
       <c r="A11" s="207"/>
       <c r="B11" s="76" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C11" s="77" t="str">
         <f>IF($O34&gt;2.49%,"No","Yes")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
@@ -26513,11 +26513,11 @@
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="77" t="str">
         <f>IF($O32&gt;21.99%,"No","Yes")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
@@ -26624,11 +26624,11 @@
       <c r="M15" s="251"/>
       <c r="N15" s="91">
         <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="O15" s="92">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P15" s="93" t="s">
         <v>1</v>
@@ -26663,11 +26663,11 @@
       </c>
       <c r="G16" s="99"/>
       <c r="H16" s="100">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>0</v>
+        <v>6295.5</v>
       </c>
       <c r="J16" s="102">
         <v>0</v>
@@ -26678,23 +26678,23 @@
       </c>
       <c r="L16" s="104">
         <f>I16*14%</f>
-        <v>0</v>
+        <v>881.37000000000012</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>0</v>
+        <v>5414.13</v>
       </c>
       <c r="N16" s="105">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>0</v>
+        <v>974.54340000000002</v>
       </c>
       <c r="O16" s="106">
         <f>(N16+M16)*$O$15</f>
-        <v>0</v>
+        <v>31.943366999999999</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>0</v>
+        <v>6420.6167669999995</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="XFD16" t="s">
@@ -26727,11 +26727,11 @@
       </c>
       <c r="G17" s="113"/>
       <c r="H17" s="114">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
-        <v>0</v>
+        <v>6295.5</v>
       </c>
       <c r="J17" s="116">
         <v>0</v>
@@ -26742,23 +26742,23 @@
       </c>
       <c r="L17" s="104">
         <f t="shared" ref="L17:L21" si="4">I17*14%</f>
-        <v>0</v>
+        <v>881.37000000000012</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>0</v>
+        <v>5414.13</v>
       </c>
       <c r="N17" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>974.54340000000002</v>
       </c>
       <c r="O17" s="118">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>0</v>
+        <v>31.943366999999999</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6420.6167669999995</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -26851,11 +26851,11 @@
       </c>
       <c r="G19" s="113"/>
       <c r="H19" s="114">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11622.4</v>
       </c>
       <c r="J19" s="116">
         <v>0</v>
@@ -26866,23 +26866,23 @@
       </c>
       <c r="L19" s="104">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1627.1360000000002</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>9995.2639999999992</v>
       </c>
       <c r="N19" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1799.1475199999998</v>
       </c>
       <c r="O19" s="118">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>58.972057599999999</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11853.3835776</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26971,11 +26971,11 @@
       </c>
       <c r="G21" s="113"/>
       <c r="H21" s="114">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11622.4</v>
       </c>
       <c r="J21" s="116">
         <v>0</v>
@@ -26986,23 +26986,23 @@
       </c>
       <c r="L21" s="104">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1627.1360000000002</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>9995.2639999999992</v>
       </c>
       <c r="N21" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1799.1475199999998</v>
       </c>
       <c r="O21" s="118">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>58.972057599999999</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11853.3835776</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27190,11 +27190,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>35835.800000000003</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
@@ -27203,23 +27203,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5017.0120000000006</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>30818.787999999997</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>0</v>
+        <v>5547.3818399999991</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>0</v>
+        <v>181.83084919999999</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>0</v>
+        <v>36548.000689199995</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27269,7 +27269,7 @@
       <c r="O28" s="239"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>0</v>
+        <v>35835.800000000003</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27290,7 +27290,7 @@
       <c r="O29" s="241"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>0</v>
+        <v>5017.0120000000006</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27333,7 +27333,7 @@
       <c r="O31" s="241"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>0</v>
+        <v>30818.788</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27354,11 +27354,11 @@
       </c>
       <c r="O32" s="155">
         <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>0</v>
+        <v>5547.3818399999991</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27380,7 +27380,7 @@
       <c r="O33" s="243"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>0</v>
+        <v>36366.169840000002</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27401,11 +27401,11 @@
       </c>
       <c r="O34" s="158">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>0</v>
+        <v>181.83084920000002</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27415,7 +27415,7 @@
       <c r="O35" s="221"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>0</v>
+        <v>36548.000689200002</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27587,7 +27587,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -27602,7 +27602,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -27615,7 +27615,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -27624,7 +27624,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -27708,7 +27708,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="168" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -28831,7 +28831,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -28846,7 +28846,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -28859,7 +28859,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -28868,7 +28868,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -28952,7 +28952,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -30076,7 +30076,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -30091,7 +30091,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -30104,7 +30104,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -30113,7 +30113,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -30197,7 +30197,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="168" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -31322,7 +31322,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -31337,7 +31337,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="247" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="247"/>
       <c r="C5" s="247"/>
@@ -31350,7 +31350,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -31359,7 +31359,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="202" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -31443,7 +31443,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
